--- a/output_data/charts/0500000US39097.xlsx
+++ b/output_data/charts/0500000US39097.xlsx
@@ -234,7 +234,7 @@
                   <c:v>43724</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>43849</c:v>
+                  <c:v>43858</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1002,7 +1002,7 @@
         <v>44013</v>
       </c>
       <c r="B6" s="2">
-        <v>43849</v>
+        <v>43858</v>
       </c>
     </row>
     <row r="7" spans="1:5">
